--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 днрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/06,07,26 Останкино КИ/дв 06,07,26 днрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\06,07,26 Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA822DF-F4A5-412C-9675-050F4608BBCD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FD5242-97EE-43B5-857C-869FE46EFB2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$111</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="160">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>3986 Ароматная с/к в/у 1/250 ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>вместо 5706</t>
   </si>
   <si>
     <t>4063 МЯСНАЯ Папа может вар п/о_Л   ОСТАНКИНО</t>
@@ -488,6 +485,33 @@
   <si>
     <t>13,07,</t>
   </si>
+  <si>
+    <t>7647  ХОЧУ ВЕТЧ. ИЗ СВИН.ОТРУБА с/н мгс 1/100</t>
+  </si>
+  <si>
+    <t>7651  ХОЧУ ВЕТЧ. МРАМОР. ПМ с/н мгс 1/100_Л11</t>
+  </si>
+  <si>
+    <t>7299  НАБОР ДЛЯ ПИЦЦЫ Папа Может с/к в/у</t>
+  </si>
+  <si>
+    <t>новинка</t>
+  </si>
+  <si>
+    <t>ротация на 1001062507616,ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001061977613,АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <t>ротация на 1001304197608,СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+  </si>
+  <si>
+    <t>плюсом 5 дней</t>
+  </si>
+  <si>
+    <t>вместо 5706 / плюсом 5 дней</t>
+  </si>
 </sst>
 </file>
 
@@ -508,17 +532,23 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -530,6 +560,8 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -1129,10 +1161,10 @@
         <v>16</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>17</v>
@@ -1211,10 +1243,10 @@
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="T4" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>151</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
@@ -1238,10 +1270,10 @@
       </c>
       <c r="AC4" s="8"/>
       <c r="AD4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE4" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="AE4" s="8" t="s">
-        <v>151</v>
       </c>
       <c r="AF4" s="8"/>
       <c r="AG4" s="8"/>
@@ -1312,7 +1344,7 @@
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>10382</v>
+        <v>10932</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
@@ -1347,7 +1379,7 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="3">
         <f>SUM(AD6:AD498)</f>
-        <v>5202.17</v>
+        <v>5302.17</v>
       </c>
       <c r="AE5" s="3">
         <f>SUM(AE6:AE498)</f>
@@ -1568,7 +1600,9 @@
       <c r="AB7" s="8">
         <v>1.5744</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="AD7" s="8">
         <f t="shared" ref="AD7:AD70" si="8">G7*S7</f>
         <v>0</v>
@@ -1683,7 +1717,7 @@
         <v>55.2</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="AD8" s="8">
         <f t="shared" si="8"/>
@@ -1713,7 +1747,7 @@
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>33</v>
@@ -1831,7 +1865,7 @@
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>33</v>
@@ -1911,7 +1945,7 @@
         <v>3.8715999999999999</v>
       </c>
       <c r="AC10" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD10" s="8">
         <f t="shared" si="8"/>
@@ -1941,7 +1975,7 @@
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>33</v>
@@ -2053,7 +2087,7 @@
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>33</v>
@@ -2171,7 +2205,7 @@
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>31</v>
@@ -2250,7 +2284,9 @@
       <c r="AB13" s="8">
         <v>14.2</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="AD13" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -2279,7 +2315,7 @@
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>33</v>
@@ -2394,7 +2430,7 @@
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>31</v>
@@ -2476,7 +2512,7 @@
         <v>20.2</v>
       </c>
       <c r="AC15" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD15" s="8">
         <f t="shared" si="8"/>
@@ -2506,7 +2542,7 @@
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>31</v>
@@ -2528,7 +2564,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8">
@@ -2591,7 +2627,7 @@
         <v>74.8</v>
       </c>
       <c r="AC16" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AD16" s="8">
         <f t="shared" si="8"/>
@@ -2621,7 +2657,7 @@
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>33</v>
@@ -2736,7 +2772,7 @@
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>33</v>
@@ -2818,7 +2854,9 @@
       <c r="AB18" s="8">
         <v>9.8799999999999999E-2</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="AD18" s="8">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -2847,7 +2885,7 @@
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>31</v>
@@ -2963,7 +3001,7 @@
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>33</v>
@@ -3079,7 +3117,7 @@
     </row>
     <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>31</v>
@@ -3164,7 +3202,9 @@
       <c r="AB21" s="8">
         <v>17.399999999999999</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="AD21" s="8">
         <f t="shared" si="8"/>
         <v>28.16</v>
@@ -3193,7 +3233,7 @@
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>33</v>
@@ -3302,7 +3342,7 @@
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>31</v>
@@ -3382,7 +3422,7 @@
         <v>4</v>
       </c>
       <c r="AC23" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD23" s="8">
         <f t="shared" si="8"/>
@@ -3412,7 +3452,7 @@
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>33</v>
@@ -3527,7 +3567,7 @@
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>31</v>
@@ -3645,7 +3685,7 @@
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>31</v>
@@ -3753,7 +3793,7 @@
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>31</v>
@@ -3771,10 +3811,10 @@
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="K27" s="10">
         <v>7</v>
@@ -3855,7 +3895,7 @@
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>31</v>
@@ -3935,7 +3975,7 @@
         <v>6.2</v>
       </c>
       <c r="AC28" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD28" s="8">
         <f t="shared" si="8"/>
@@ -3965,7 +4005,7 @@
     </row>
     <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>33</v>
@@ -4079,7 +4119,7 @@
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>31</v>
@@ -4192,7 +4232,7 @@
     </row>
     <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>31</v>
@@ -4307,7 +4347,7 @@
     </row>
     <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>31</v>
@@ -4418,7 +4458,7 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>31</v>
@@ -4536,7 +4576,7 @@
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>31</v>
@@ -4559,8 +4599,8 @@
       <c r="H34" s="8">
         <v>60</v>
       </c>
-      <c r="I34" s="8">
-        <v>6453</v>
+      <c r="I34" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
@@ -4625,7 +4665,9 @@
       <c r="AB34" s="8">
         <v>47.6</v>
       </c>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="AD34" s="8">
         <f t="shared" si="8"/>
         <v>20.6</v>
@@ -4654,7 +4696,7 @@
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>31</v>
@@ -4677,8 +4719,8 @@
       <c r="H35" s="8">
         <v>60</v>
       </c>
-      <c r="I35" s="8">
-        <v>6454</v>
+      <c r="I35" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
@@ -4740,7 +4782,9 @@
       <c r="AB35" s="8">
         <v>48.2</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8" t="s">
+        <v>156</v>
+      </c>
       <c r="AD35" s="8">
         <f t="shared" si="8"/>
         <v>12.8</v>
@@ -4769,7 +4813,7 @@
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>31</v>
@@ -4792,8 +4836,8 @@
       <c r="H36" s="8">
         <v>45</v>
       </c>
-      <c r="I36" s="8">
-        <v>6459</v>
+      <c r="I36" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8">
@@ -4848,7 +4892,9 @@
       <c r="AB36" s="8">
         <v>13.2</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="AD36" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -4877,7 +4923,7 @@
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>33</v>
@@ -4986,7 +5032,7 @@
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>31</v>
@@ -5094,7 +5140,7 @@
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>31</v>
@@ -5202,7 +5248,7 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>33</v>
@@ -5317,7 +5363,7 @@
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>33</v>
@@ -5428,7 +5474,7 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>33</v>
@@ -5543,7 +5589,7 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>33</v>
@@ -5655,7 +5701,7 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>31</v>
@@ -5673,7 +5719,7 @@
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J44" s="10"/>
       <c r="K44" s="10">
@@ -5757,7 +5803,7 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>31</v>
@@ -5837,7 +5883,7 @@
         <v>75.2</v>
       </c>
       <c r="AC45" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD45" s="8">
         <f t="shared" si="8"/>
@@ -5867,7 +5913,7 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>33</v>
@@ -5975,7 +6021,7 @@
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>31</v>
@@ -6093,7 +6139,7 @@
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>31</v>
@@ -6206,7 +6252,7 @@
     </row>
     <row r="49" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>31</v>
@@ -6317,7 +6363,7 @@
     </row>
     <row r="50" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>33</v>
@@ -6335,7 +6381,7 @@
       </c>
       <c r="H50" s="10"/>
       <c r="I50" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J50" s="10"/>
       <c r="K50" s="10">
@@ -6419,7 +6465,7 @@
     </row>
     <row r="51" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>31</v>
@@ -6537,7 +6583,7 @@
     </row>
     <row r="52" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>31</v>
@@ -6650,7 +6696,7 @@
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>31</v>
@@ -6668,10 +6714,10 @@
       </c>
       <c r="H53" s="10"/>
       <c r="I53" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="J53" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="K53" s="10">
         <v>122</v>
@@ -6754,7 +6800,7 @@
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>31</v>
@@ -6836,7 +6882,7 @@
         <v>40.200000000000003</v>
       </c>
       <c r="AC54" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD54" s="8">
         <f t="shared" si="8"/>
@@ -6866,7 +6912,7 @@
     </row>
     <row r="55" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>31</v>
@@ -6946,7 +6992,7 @@
         <v>4.8</v>
       </c>
       <c r="AC55" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD55" s="8">
         <f t="shared" si="8"/>
@@ -6976,7 +7022,7 @@
     </row>
     <row r="56" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>33</v>
@@ -7088,7 +7134,7 @@
     </row>
     <row r="57" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>33</v>
@@ -7199,7 +7245,7 @@
     </row>
     <row r="58" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>31</v>
@@ -7303,7 +7349,7 @@
     </row>
     <row r="59" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>31</v>
@@ -7411,7 +7457,7 @@
     </row>
     <row r="60" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>33</v>
@@ -7519,7 +7565,7 @@
     </row>
     <row r="61" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>33</v>
@@ -7630,7 +7676,7 @@
     </row>
     <row r="62" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>31</v>
@@ -7734,7 +7780,7 @@
     </row>
     <row r="63" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>31</v>
@@ -7752,7 +7798,7 @@
       </c>
       <c r="H63" s="10"/>
       <c r="I63" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J63" s="10"/>
       <c r="K63" s="10">
@@ -7836,7 +7882,7 @@
     </row>
     <row r="64" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>33</v>
@@ -7945,7 +7991,7 @@
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>31</v>
@@ -8029,7 +8075,9 @@
       <c r="AB65" s="8">
         <v>8</v>
       </c>
-      <c r="AC65" s="8"/>
+      <c r="AC65" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="AD65" s="8">
         <f t="shared" si="8"/>
         <v>10.5</v>
@@ -8058,7 +8106,7 @@
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>33</v>
@@ -8169,7 +8217,7 @@
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>31</v>
@@ -8280,7 +8328,7 @@
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>31</v>
@@ -8398,7 +8446,7 @@
     </row>
     <row r="69" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>31</v>
@@ -8420,10 +8468,10 @@
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K69" s="10">
         <v>1210</v>
@@ -8506,7 +8554,7 @@
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>33</v>
@@ -8623,7 +8671,7 @@
     </row>
     <row r="71" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>31</v>
@@ -8734,7 +8782,7 @@
     </row>
     <row r="72" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>31</v>
@@ -8758,7 +8806,7 @@
         <v>50</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="8">
@@ -8823,7 +8871,7 @@
         <v>136.80000000000001</v>
       </c>
       <c r="AC72" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AD72" s="8">
         <f t="shared" si="33"/>
@@ -8853,7 +8901,7 @@
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>33</v>
@@ -8871,10 +8919,10 @@
       </c>
       <c r="H73" s="10"/>
       <c r="I73" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K73" s="10">
         <v>7.5</v>
@@ -8955,7 +9003,7 @@
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>33</v>
@@ -9070,7 +9118,7 @@
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>31</v>
@@ -9176,7 +9224,7 @@
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>31</v>
@@ -9294,7 +9342,7 @@
     </row>
     <row r="77" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>31</v>
@@ -9373,7 +9421,9 @@
       <c r="AB77" s="8">
         <v>5.2</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="AD77" s="8">
         <f t="shared" si="33"/>
         <v>0</v>
@@ -9402,7 +9452,7 @@
     </row>
     <row r="78" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>31</v>
@@ -9420,7 +9470,7 @@
       </c>
       <c r="H78" s="10"/>
       <c r="I78" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J78" s="10"/>
       <c r="K78" s="10">
@@ -9504,7 +9554,7 @@
     </row>
     <row r="79" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>31</v>
@@ -9622,7 +9672,7 @@
     </row>
     <row r="80" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>33</v>
@@ -9737,7 +9787,7 @@
     </row>
     <row r="81" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>31</v>
@@ -9841,7 +9891,7 @@
     </row>
     <row r="82" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>33</v>
@@ -9956,7 +10006,7 @@
     </row>
     <row r="83" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>31</v>
@@ -10074,7 +10124,7 @@
     </row>
     <row r="84" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>31</v>
@@ -10187,7 +10237,7 @@
     </row>
     <row r="85" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>31</v>
@@ -10267,7 +10317,7 @@
         <v>9.6</v>
       </c>
       <c r="AC85" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD85" s="8">
         <f t="shared" si="33"/>
@@ -10297,7 +10347,7 @@
     </row>
     <row r="86" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>31</v>
@@ -10412,7 +10462,7 @@
     </row>
     <row r="87" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>31</v>
@@ -10525,7 +10575,7 @@
     </row>
     <row r="88" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>31</v>
@@ -10636,7 +10686,7 @@
     </row>
     <row r="89" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>31</v>
@@ -10750,7 +10800,7 @@
     </row>
     <row r="90" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>31</v>
@@ -10862,7 +10912,7 @@
     </row>
     <row r="91" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>33</v>
@@ -10880,7 +10930,7 @@
       </c>
       <c r="H91" s="10"/>
       <c r="I91" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J91" s="10"/>
       <c r="K91" s="10">
@@ -10964,7 +11014,7 @@
     </row>
     <row r="92" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>31</v>
@@ -11044,7 +11094,7 @@
         <v>13.6</v>
       </c>
       <c r="AC92" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD92" s="8">
         <f t="shared" si="33"/>
@@ -11074,7 +11124,7 @@
     </row>
     <row r="93" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>31</v>
@@ -11182,7 +11232,7 @@
     </row>
     <row r="94" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>31</v>
@@ -11292,7 +11342,7 @@
     </row>
     <row r="95" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>31</v>
@@ -11403,7 +11453,7 @@
     </row>
     <row r="96" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>31</v>
@@ -11483,7 +11533,7 @@
         <v>3.4</v>
       </c>
       <c r="AC96" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD96" s="8">
         <f t="shared" si="33"/>
@@ -11513,7 +11563,7 @@
     </row>
     <row r="97" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>31</v>
@@ -11623,7 +11673,7 @@
     </row>
     <row r="98" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>31</v>
@@ -11647,7 +11697,7 @@
         <v>60</v>
       </c>
       <c r="I98" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="8">
@@ -11711,7 +11761,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="AC98" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AD98" s="8">
         <f t="shared" si="33"/>
@@ -11741,7 +11791,7 @@
     </row>
     <row r="99" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>31</v>
@@ -11855,7 +11905,7 @@
     </row>
     <row r="100" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>31</v>
@@ -11961,7 +12011,7 @@
     </row>
     <row r="101" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>31</v>
@@ -12073,7 +12123,7 @@
     </row>
     <row r="102" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>31</v>
@@ -12091,7 +12141,7 @@
       </c>
       <c r="H102" s="10"/>
       <c r="I102" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J102" s="10"/>
       <c r="K102" s="10">
@@ -12177,7 +12227,7 @@
     </row>
     <row r="103" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>33</v>
@@ -12257,7 +12307,7 @@
         <v>2.8502000000000001</v>
       </c>
       <c r="AC103" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AD103" s="8">
         <f t="shared" si="33"/>
@@ -12287,7 +12337,7 @@
     </row>
     <row r="104" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>31</v>
@@ -12369,7 +12419,7 @@
         <v>0</v>
       </c>
       <c r="AC104" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AD104" s="8">
         <f t="shared" si="33"/>
@@ -12399,7 +12449,7 @@
     </row>
     <row r="105" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>31</v>
@@ -12417,7 +12467,7 @@
       </c>
       <c r="H105" s="10"/>
       <c r="I105" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J105" s="10"/>
       <c r="K105" s="10">
@@ -12501,7 +12551,7 @@
     </row>
     <row r="106" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>33</v>
@@ -12519,10 +12569,10 @@
       </c>
       <c r="H106" s="10"/>
       <c r="I106" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="10">
@@ -12601,7 +12651,7 @@
     </row>
     <row r="107" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>31</v>
@@ -12621,14 +12671,12 @@
       <c r="G107" s="11">
         <v>0</v>
       </c>
-      <c r="H107" s="10">
-        <v>0</v>
-      </c>
+      <c r="H107" s="10"/>
       <c r="I107" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K107" s="10">
         <v>15</v>
@@ -12709,7 +12757,7 @@
     </row>
     <row r="108" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>33</v>
@@ -12729,14 +12777,12 @@
       <c r="G108" s="11">
         <v>0</v>
       </c>
-      <c r="H108" s="10">
-        <v>0</v>
-      </c>
+      <c r="H108" s="10"/>
       <c r="I108" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K108" s="10">
         <v>40.799999999999997</v>
@@ -12816,15 +12862,23 @@
       <c r="AV108" s="8"/>
     </row>
     <row r="109" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
+      <c r="A109" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
-      <c r="G109" s="6"/>
+      <c r="G109" s="6">
+        <v>0.1</v>
+      </c>
       <c r="H109" s="8"/>
-      <c r="I109" s="8"/>
+      <c r="I109" s="8">
+        <v>7647</v>
+      </c>
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
@@ -12832,20 +12886,40 @@
       <c r="N109" s="8"/>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
-      <c r="Q109" s="8"/>
+      <c r="Q109" s="8">
+        <v>0</v>
+      </c>
       <c r="R109" s="8"/>
-      <c r="S109" s="8"/>
-      <c r="T109" s="8"/>
+      <c r="S109" s="8">
+        <v>250</v>
+      </c>
       <c r="U109" s="8"/>
       <c r="V109" s="8"/>
-      <c r="W109" s="8"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="8"/>
-      <c r="Z109" s="8"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
-      <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
+      <c r="W109" s="8">
+        <v>0</v>
+      </c>
+      <c r="X109" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD109" s="8">
+        <f>G109*S109</f>
+        <v>25</v>
+      </c>
       <c r="AE109" s="8"/>
       <c r="AF109" s="8"/>
       <c r="AG109" s="8"/>
@@ -12866,15 +12940,23 @@
       <c r="AV109" s="8"/>
     </row>
     <row r="110" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
+      <c r="A110" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
-      <c r="G110" s="6"/>
+      <c r="G110" s="6">
+        <v>0.1</v>
+      </c>
       <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
+      <c r="I110" s="8">
+        <v>7651</v>
+      </c>
       <c r="J110" s="8"/>
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
@@ -12882,20 +12964,40 @@
       <c r="N110" s="8"/>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
-      <c r="Q110" s="8"/>
+      <c r="Q110" s="8">
+        <v>0</v>
+      </c>
       <c r="R110" s="8"/>
-      <c r="S110" s="8"/>
-      <c r="T110" s="8"/>
+      <c r="S110" s="8">
+        <v>250</v>
+      </c>
       <c r="U110" s="8"/>
       <c r="V110" s="8"/>
-      <c r="W110" s="8"/>
-      <c r="X110" s="8"/>
-      <c r="Y110" s="8"/>
-      <c r="Z110" s="8"/>
-      <c r="AA110" s="8"/>
-      <c r="AB110" s="8"/>
-      <c r="AC110" s="8"/>
-      <c r="AD110" s="8"/>
+      <c r="W110" s="8">
+        <v>0</v>
+      </c>
+      <c r="X110" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD110" s="8">
+        <f>G110*S110</f>
+        <v>25</v>
+      </c>
       <c r="AE110" s="8"/>
       <c r="AF110" s="8"/>
       <c r="AG110" s="8"/>
@@ -12916,15 +13018,23 @@
       <c r="AV110" s="8"/>
     </row>
     <row r="111" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
+      <c r="A111" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
-      <c r="G111" s="6"/>
+      <c r="G111" s="6">
+        <v>1</v>
+      </c>
       <c r="H111" s="8"/>
-      <c r="I111" s="8"/>
+      <c r="I111" s="8">
+        <v>7299</v>
+      </c>
       <c r="J111" s="8"/>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -12932,20 +13042,40 @@
       <c r="N111" s="8"/>
       <c r="O111" s="8"/>
       <c r="P111" s="8"/>
-      <c r="Q111" s="8"/>
+      <c r="Q111" s="8">
+        <v>0</v>
+      </c>
       <c r="R111" s="8"/>
-      <c r="S111" s="8"/>
-      <c r="T111" s="8"/>
+      <c r="S111" s="8">
+        <v>50</v>
+      </c>
       <c r="U111" s="8"/>
       <c r="V111" s="8"/>
-      <c r="W111" s="8"/>
-      <c r="X111" s="8"/>
-      <c r="Y111" s="8"/>
-      <c r="Z111" s="8"/>
-      <c r="AA111" s="8"/>
-      <c r="AB111" s="8"/>
-      <c r="AC111" s="8"/>
-      <c r="AD111" s="8"/>
+      <c r="W111" s="8">
+        <v>0</v>
+      </c>
+      <c r="X111" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD111" s="8">
+        <f>G111*S111</f>
+        <v>50</v>
+      </c>
       <c r="AE111" s="8"/>
       <c r="AF111" s="8"/>
       <c r="AG111" s="8"/>
@@ -32316,7 +32446,7 @@
       <c r="AV498" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD108" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AD111" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
